--- a/Trading Analysis/Vortex Matches/output/1130895_No Prices.xlsx
+++ b/Trading Analysis/Vortex Matches/output/1130895_No Prices.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="103">
   <si>
     <t>RFQ Number</t>
   </si>
@@ -277,9 +277,6 @@
     <t>VQ</t>
   </si>
   <si>
-    <t>Global Sourcing</t>
-  </si>
-  <si>
     <t>Braun Electronic Components</t>
   </si>
   <si>
@@ -292,16 +289,10 @@
     <t>Cross Components, Inc.</t>
   </si>
   <si>
-    <t>Non-Traceable without Franchised lines</t>
-  </si>
-  <si>
     <t>Atlantic Semiconductor</t>
   </si>
   <si>
     <t>LM2591HVSX-5.0/NOPB</t>
-  </si>
-  <si>
-    <t>New/Ungraded Vendor</t>
   </si>
   <si>
     <t>Monash Technologies &amp; Supplies</t>
@@ -6603,13 +6594,13 @@
         <v>87</v>
       </c>
       <c r="I111" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J111" t="s">
         <v>86</v>
       </c>
       <c r="K111" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L111" s="2">
         <v>0</v>
@@ -6656,13 +6647,13 @@
         <v>87</v>
       </c>
       <c r="I112" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J112" t="s">
         <v>65</v>
       </c>
       <c r="K112" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L112" s="2">
         <v>0</v>
@@ -6715,7 +6706,7 @@
         <v>57</v>
       </c>
       <c r="K113" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L113" s="2">
         <v>0</v>
@@ -6762,13 +6753,13 @@
         <v>87</v>
       </c>
       <c r="I114" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J114" t="s">
         <v>57</v>
       </c>
       <c r="K114" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L114" s="2">
         <v>0</v>
@@ -6815,13 +6806,13 @@
         <v>87</v>
       </c>
       <c r="I115" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="J115" t="s">
         <v>66</v>
       </c>
       <c r="K115" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L115" s="2">
         <v>0</v>
@@ -6853,7 +6844,7 @@
         <v>18</v>
       </c>
       <c r="D116" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E116" s="2">
         <v>31500</v>
@@ -6868,13 +6859,13 @@
         <v>87</v>
       </c>
       <c r="I116" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="J116" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K116" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L116" s="2">
         <v>0</v>
@@ -6906,7 +6897,7 @@
         <v>18</v>
       </c>
       <c r="D117" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E117" s="2">
         <v>31000</v>
@@ -6921,13 +6912,13 @@
         <v>87</v>
       </c>
       <c r="I117" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J117" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K117" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="L117" s="2">
         <v>0</v>
@@ -6974,13 +6965,13 @@
         <v>87</v>
       </c>
       <c r="I118" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J118" t="s">
         <v>38</v>
       </c>
       <c r="K118" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L118" s="2">
         <v>0</v>
@@ -7012,7 +7003,7 @@
         <v>18</v>
       </c>
       <c r="D119" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E119" s="2">
         <v>25000</v>
@@ -7027,13 +7018,13 @@
         <v>87</v>
       </c>
       <c r="I119" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J119" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K119" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L119" s="2">
         <v>1000</v>
@@ -7042,7 +7033,7 @@
         <v>20</v>
       </c>
       <c r="N119" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="O119" s="1">
         <v>46058.2224793287</v>
@@ -7065,7 +7056,7 @@
         <v>18</v>
       </c>
       <c r="D120" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E120" s="2">
         <v>37200</v>
@@ -7080,13 +7071,13 @@
         <v>87</v>
       </c>
       <c r="I120" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="J120" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K120" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L120" s="2">
         <v>9000</v>
@@ -7095,7 +7086,7 @@
         <v>20</v>
       </c>
       <c r="N120" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="O120" s="1">
         <v>46058.22246928241</v>
